--- a/docs-数据采集与埋点/一方平台开发基线/Looply-v1.4-公共基础字段需求定稿-v1.1.xlsx
+++ b/docs-数据采集与埋点/一方平台开发基线/Looply-v1.4-公共基础字段需求定稿-v1.1.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公共字段总表" sheetId="1" r:id="Radd84be3650544c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="兼容边界" sheetId="2" r:id="R2b5c4b7205424704"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公共规则" sheetId="3" r:id="R282305cbaaed4c7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公共字段总表" sheetId="1" r:id="R113095b5da564f05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="兼容边界" sheetId="2" r:id="R3fd18f05a1ea4e39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公共规则" sheetId="3" r:id="R3de4e484f1ed4c7c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1727,19 +1727,19 @@
         <x:v>订单／支付／退款权威事实</x:v>
       </x:c>
       <x:c r="B14" t="str">
-        <x:v>由数据平台读取权威业务表形成一方分析事实，不由Web／SDK或支付服务新增埋点事件。</x:v>
+        <x:v>不属于Web／SDK或公共字段范围；完整定义见《Looply 订单与交易数据接入需求 v1.0》。</x:v>
       </x:c>
       <x:c r="C14" t="str">
-        <x:v>业务表中的原始权威事实及唯一业务键。</x:v>
+        <x:v>客户端埋点基线只保留Web边界</x:v>
       </x:c>
       <x:c r="D14" t="str">
-        <x:v>允许数据平台按独立接入任务建立同步、映射和质量规则。</x:v>
+        <x:v>由报表数据接入／数仓任务按权威文档实施</x:v>
       </x:c>
       <x:c r="E14" t="str">
-        <x:v>不得纳入Web／SDK YAML Schema，不得要求前端生成payment_failed或使用客户端failure_type代替支付失败分类。</x:v>
+        <x:v>不得纳入Web／SDK YAML Schema或要求前端生成交易事实</x:v>
       </x:c>
       <x:c r="F14" t="str">
-        <x:v>避免把数据平台业务表接入问题误判为前端埋点阻塞。</x:v>
+        <x:v>避免在客户端材料中平行维护交易字段定义</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1915,7 +1915,7 @@
         <x:v>权威业务表事实</x:v>
       </x:c>
       <x:c r="B15" t="str">
-        <x:v>order_created / payment_started / payment_failed / purchase / refund不属于Web／SDK公共字段或客户端事件；由数据平台读取订单、支付、退款权威业务表形成，完整边界见《Looply 一方埋点公共实施规则 v1.6》第七章。</x:v>
+        <x:v>order_created / payment_started / payment_failed / purchase / refund不属于Web／SDK公共字段或客户端事件；完整来源、唯一键、字段与接入要求见《Looply 订单与交易数据接入需求 v1.0》。</x:v>
       </x:c>
       <x:c r="C15" t="str">
         <x:v>已定</x:v>
